--- a/api/templates/mtb_detected_rr_detected/mw/fr.xlsx
+++ b/api/templates/mtb_detected_rr_detected/mw/fr.xlsx
@@ -1,13 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10531"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8329EA6F-C412-EF48-9A28-50E4FEF4087F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Results" state="visible" r:id="rId4"/>
+    <sheet name="Results" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
@@ -70,11 +71,11 @@
     <t>Nom du dosage</t>
   </si>
   <si>
-    <t xml:space="preserve">Date de 
+    <t>Date de 
 Prélèvement d’échantillons</t>
   </si>
   <si>
-    <t xml:space="preserve">Date de réception
+    <t>Date de réception
  en laboratoire</t>
   </si>
   <si>
@@ -156,60 +157,65 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="dd-mm-yyyy;@"/>
+    <numFmt numFmtId="164" formatCode="dd\-mm\-yyyy;@"/>
   </numFmts>
   <fonts count="9" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="11"/>
       <color indexed="64"/>
-      <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
-      <family val="2"/>
       <sz val="16"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
+      <sz val="16"/>
       <color indexed="64"/>
-      <sz val="16"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="12"/>
       <color indexed="64"/>
-      <sz val="12"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
-      <family val="2"/>
       <sz val="12"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -235,17 +241,33 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium"/>
-      <right style="medium"/>
-      <top style="medium"/>
-      <bottom style="medium"/>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -514,15 +536,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S12"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.2" defaultColWidth="8.83203125"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:S10"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5" customWidth="1"/>
     <col min="2" max="4" width="24.1640625" customWidth="1"/>
     <col min="5" max="5" width="23.1640625" customWidth="1"/>
     <col min="6" max="6" width="15.83203125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="28" customWidth="1"/>
+    <col min="7" max="7" width="13.33203125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="25" customWidth="1"/>
     <col min="9" max="9" width="28" customWidth="1"/>
     <col min="10" max="14" width="18.5" customWidth="1"/>
@@ -531,7 +553,7 @@
     <col min="19" max="19" width="60.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -553,7 +575,7 @@
       <c r="Q1" s="3"/>
       <c r="R1" s="3"/>
     </row>
-    <row r="2" ht="16" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
         <v>1</v>
       </c>
@@ -575,7 +597,7 @@
       <c r="Q2" s="6"/>
       <c r="R2" s="6"/>
     </row>
-    <row r="3" ht="16" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -597,7 +619,7 @@
       <c r="Q3" s="6"/>
       <c r="R3" s="6"/>
     </row>
-    <row r="4" ht="16" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -619,7 +641,7 @@
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
     </row>
-    <row r="5" ht="16" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -641,7 +663,7 @@
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
     </row>
-    <row r="6" ht="16" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="6"/>
       <c r="C6" s="6"/>
       <c r="D6" s="6"/>
@@ -660,7 +682,7 @@
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
     </row>
-    <row r="7" ht="16" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="6" t="s">
         <v>5</v>
       </c>
@@ -681,7 +703,7 @@
       <c r="Q7" s="6"/>
       <c r="R7" s="6"/>
     </row>
-    <row r="8" ht="16" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="8" t="s">
         <v>6</v>
       </c>
@@ -705,7 +727,7 @@
       <c r="Q8" s="6"/>
       <c r="R8" s="7"/>
     </row>
-    <row r="9" ht="31" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" ht="31" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="9" t="s">
         <v>7</v>
       </c>
@@ -764,7 +786,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" ht="16" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="14" t="s">
         <v>26</v>
       </c>
@@ -823,10 +845,8 @@
         <v>44</v>
       </c>
     </row>
-    <row r="11" spans="8:19" x14ac:dyDescent="0.25"/>
-    <row r="12" spans="8:19" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.5118110236220469" footer="0.5118110236220469"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51181102362204689" footer="0.51181102362204689"/>
+  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>